--- a/reports/二级子公司D_利润表_2026-03.xlsx
+++ b/reports/二级子公司D_利润表_2026-03.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>85498041</v>
+        <v>87679037</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>83594631</v>
+        <v>83933262</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>230904397</v>
+        <v>230718984</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>287703</v>
+        <v>289644</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>796193</v>
+        <v>799663</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>248639</v>
+        <v>247749</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>682403</v>
+        <v>685194</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>206095</v>
+        <v>205947</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>568374</v>
+        <v>570374</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>184292</v>
+        <v>184900</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>511662</v>
+        <v>512490</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>103159</v>
+        <v>102520</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>284380</v>
+        <v>284169</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>82850</v>
+        <v>81922</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>227415</v>
+        <v>226913</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>84385303</v>
+        <v>86566355</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>82481893</v>
+        <v>82820580</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4657385</v>
+        <v>4620165</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>12796307</v>
+        <v>12734666</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>361473</v>
+        <v>360198</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>994732</v>
+        <v>991252</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>614455</v>
+        <v>619034</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1705328</v>
+        <v>1701748</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>74102779</v>
+        <v>74448422</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>204746746</v>
+        <v>204587745</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1243410</v>
+        <v>1242700</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>3411698</v>
+        <v>3416372</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>411488</v>
+        <v>414471</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1136720</v>
+        <v>1140688</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2048509</v>
+        <v>2071373</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>5685707</v>
+        <v>5709793</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>516605</v>
+        <v>517097</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1421891</v>
+        <v>1427972</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1862401</v>
+        <v>1857533</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>5116350</v>
+        <v>5138418</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>41009</v>
+        <v>41175</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>123588</v>
+        <v>123990</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1109072</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>3074182</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>737995</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2045494</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>56225339</v>
+        <v>59905189</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>50418535</v>
+        <v>50126679</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>49486265</v>
+        <v>49202377</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>136502023</v>
+        <v>135831741</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>932270</v>
+        <v>924302</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>2558519</v>
+        <v>2547086</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1853069</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>5098677</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>594463</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1634053</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>372335</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1023204</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>447433</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1230194</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>335721</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>924129</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>223677</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>616716</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>186108</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>514063</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>874951</v>
+        <v>876886</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>2415545</v>
+        <v>2426190</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>665632</v>
+        <v>668877</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1847787</v>
+        <v>1852983</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>516322</v>
+        <v>513311</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1421900</v>
+        <v>1422874</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3933236</v>
+        <v>3894227</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>10801557</v>
+        <v>10792893</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>153848</v>
+        <v>153583</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>463434</v>
+        <v>425276</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>328447</v>
+        <v>327697</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>989171</v>
+        <v>984933</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>372800</v>
+        <v>327697</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1112417</v>
+        <v>984933</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41269</v>
+        <v>41092</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>123553</v>
+        <v>123046</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>166832</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>498794</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>325199</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>893833</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111727</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>333675</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83903</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>250736</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>139881</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>418563</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>465921</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1284930</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>74423</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>223510</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55690</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>167536</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92583</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>278867</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64659</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>194860</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46108</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>138915</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36858</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>110933</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27652</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>83092</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28159964</v>
+        <v>27804744</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32371005</v>
+        <v>30824762</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>185432</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>510047</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46471</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>138801</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>72264</v>
+        <v>72432</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>216218</v>
+        <v>216328</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28087700</v>
+        <v>27917744</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2574209</v>
+        <v>2590280</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>7727768</v>
+        <v>7752509</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25513491</v>
+        <v>25327464</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25513491</v>
+        <v>25327464</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25513491</v>
+        <v>25327464</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25513491</v>
+        <v>25327464</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25513491</v>
+        <v>25327464</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
